--- a/quizzes/021_si_units_quiz--quizzes.xlsx
+++ b/quizzes/021_si_units_quiz--quizzes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -676,7 +676,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Meter</t>
+          <t>Si Derived Unit 1 Form</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Prefix</t>
+          <t>Si Prefix 2 Form</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Prefix</t>
+          <t>Si Prefix 3 Form</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prefix</t>
+          <t>Si Prefix 4 Form</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Prefix</t>
+          <t>Si Prefix 5 Form</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Prefix</t>
+          <t>Si Prefix 6 Form</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Prefix</t>
+          <t>Si Prefix 7 Form</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Prefix</t>
+          <t>Si Prefix 8 Form</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,7 +929,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prefix</t>
+          <t>Si Prefix 9 Form</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Si Base Unit 4 Form</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -993,12 +993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>si_base_unit_3_form</t>
+          <t>si_base_unit_3_form_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Liter</t>
+          <t>Si Base Unit 3 Form 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
